--- a/artfynd/A 19945-2023 artfynd.xlsx
+++ b/artfynd/A 19945-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19945-2023 artfynd.xlsx
+++ b/artfynd/A 19945-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66211303</v>
+        <v>6760397</v>
       </c>
       <c r="B2" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dammhyttan, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461198.8729121244</v>
+        <v>461280</v>
       </c>
       <c r="R2" t="n">
-        <v>6629649.304074465</v>
+        <v>6629727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,29 +738,19 @@
           <t>Färnebo</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>S-Fil-0104</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>c:a 65 plantor</t>
+          <t>1990-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,40 +762,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Högörtäng med buskar</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Igenväxande ängsmark/betesmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Värmland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Jan Teodorsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Jan Teodorsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6773922</v>
+        <v>56247999</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,29 +811,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dammhyttan, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461279.8293671195</v>
+        <v>461278</v>
       </c>
       <c r="R3" t="n">
-        <v>6629726.961484636</v>
+        <v>6629722</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,34 +859,19 @@
           <t>Färnebo</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Fil-0104</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8 plantor, varav 4 blommade</t>
+          <t>Endast en blommande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,7 +886,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Värmland Floraväktarna</t>
+          <t>Jan Teodorsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -949,23 +894,14 @@
           <t>Jan Teodorsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>87331302</v>
       </c>
       <c r="B4" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461272.0753643833</v>
+        <v>461272</v>
       </c>
       <c r="R4" t="n">
-        <v>6629708.423519421</v>
+        <v>6629708</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1089,15 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56247999</v>
+        <v>66211303</v>
       </c>
       <c r="B5" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,36 +1036,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>219880</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1144,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461277.7609420464</v>
+        <v>461199</v>
       </c>
       <c r="R5" t="n">
-        <v>6629721.950947713</v>
+        <v>6629649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1174,27 +1105,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Endast en blommande</t>
+          <t>c:a 65 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,6 +1126,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Högörtäng med buskar</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Igenväxande ängsmark/betesmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 19945-2023 artfynd.xlsx
+++ b/artfynd/A 19945-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6760397</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56247999</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87331302</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,8 +1169,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66211303</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>